--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
@@ -15451,7 +15451,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Afiliación FONASA</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:52</t>
+    <t xml:space="preserve">2026-08-28 15:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:10</t>
+    <t xml:space="preserve">2026-08-29 05:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:47</t>
+    <t xml:space="preserve">2026-09-07 13:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2021.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:09</t>
+    <t xml:space="preserve">2026-09-08 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
